--- a/research/traditional_assets/database/data/tunisia/tunisia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_insurance_prop_cas.xlsx
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1085216499122428</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AB2">
-        <v>0.1085216499122428</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1085216499122428</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AB3">
-        <v>0.1085216499122428</v>
+        <v>0.1694296081871153</v>
       </c>
       <c r="AD3">
         <v>0</v>

--- a/research/traditional_assets/database/data/tunisia/tunisia_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_insurance_prop_cas.xlsx
@@ -588,28 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0196</v>
-      </c>
-      <c r="E2">
-        <v>-0.447</v>
+        <v>0.0581</v>
       </c>
       <c r="G2">
-        <v>0.08852173913043478</v>
+        <v>0.03770992366412214</v>
       </c>
       <c r="H2">
-        <v>0.08852173913043478</v>
+        <v>0.03770992366412214</v>
       </c>
       <c r="I2">
-        <v>0.006191304347826086</v>
+        <v>0.03450381679389312</v>
       </c>
       <c r="J2">
-        <v>0.00404008843036109</v>
+        <v>0.0321082150061306</v>
       </c>
       <c r="K2">
-        <v>0.232</v>
+        <v>1.79</v>
       </c>
       <c r="L2">
-        <v>0.004034782608695653</v>
+        <v>0.02732824427480916</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -639,10 +636,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.1694296081871153</v>
+        <v>0.1561208226034739</v>
       </c>
       <c r="AB2">
-        <v>0.1694296081871153</v>
+        <v>0.1561208226034739</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -692,28 +689,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0196</v>
-      </c>
-      <c r="E3">
-        <v>-0.447</v>
+        <v>0.0581</v>
       </c>
       <c r="G3">
-        <v>0.08852173913043478</v>
+        <v>0.03770992366412214</v>
       </c>
       <c r="H3">
-        <v>0.08852173913043478</v>
+        <v>0.03770992366412214</v>
       </c>
       <c r="I3">
-        <v>0.006191304347826086</v>
+        <v>0.03450381679389312</v>
       </c>
       <c r="J3">
-        <v>0.00404008843036109</v>
+        <v>0.0321082150061306</v>
       </c>
       <c r="K3">
-        <v>0.232</v>
+        <v>1.79</v>
       </c>
       <c r="L3">
-        <v>0.004034782608695653</v>
+        <v>0.02732824427480916</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1694296081871153</v>
+        <v>0.1561208226034739</v>
       </c>
       <c r="AB3">
-        <v>0.1694296081871153</v>
+        <v>0.1561208226034739</v>
       </c>
       <c r="AD3">
         <v>0</v>
